--- a/ru/downloads/data-excel/8.2.1.xlsx
+++ b/ru/downloads/data-excel/8.2.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15465" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -355,7 +355,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,6 +415,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -741,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" customWidth="1"/>
@@ -749,7 +755,7 @@
     <col min="3" max="3" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30.75" customHeight="1">
+    <row r="1" spans="1:21" ht="30.75" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
@@ -760,7 +766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -771,10 +777,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="A3" s="13"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1">
       <c r="A4" s="14" t="s">
         <v>8</v>
       </c>
@@ -835,8 +841,11 @@
       <c r="T4" s="18">
         <v>2023</v>
       </c>
+      <c r="U4" s="22">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="21" customHeight="1" thickBot="1">
+    <row r="5" spans="1:21" ht="21" customHeight="1" thickBot="1">
       <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
@@ -897,8 +906,11 @@
       <c r="T5" s="19">
         <v>105.59374642341281</v>
       </c>
+      <c r="U5" s="23">
+        <v>107.1</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="36.75" customHeight="1">
+    <row r="6" spans="1:21" ht="36.75" customHeight="1">
       <c r="A6" s="20" t="s">
         <v>12</v>
       </c>
